--- a/sampleprojects/CorporateTax/excel/states/RI_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/RI_corp.xlsx
@@ -154,7 +154,7 @@
     <t>Calculate RI tax at 7% flat rate</t>
   </si>
   <si>
-    <t>set apportionment.state_tax = apportionment.state_taxable_income * apportionment.ri_state_tax_rate; set apportionment.state_tax = the maximum of (apportionment.state_tax - apportionment.state_credits) and (0.0); set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax; add "RI tax calculated at 7% flat rate. Reference: R.I. Gen. Laws 44-11-2" to job.audit_trail;</t>
+    <t>set apportionment.state_tax = apportionment.state_taxable_income * ri_apportionment.state_tax_rate; set apportionment.state_tax = the maximum of (apportionment.state_tax - apportionment.state_credits) and (0.0); set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax; add "RI tax calculated at 7% flat rate. Reference: R.I. Gen. Laws 44-11-2" to job.audit_trail;</t>
   </si>
   <si>
     <t>Nexus but no taxable income</t>
@@ -211,13 +211,13 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>apportionment</t>
+    <t>ri_apportionment</t>
   </si>
   <si>
     <t>(3 attributes)</t>
   </si>
   <si>
-    <t>ri_economic_nexus_threshold</t>
+    <t>economic_nexus_threshold</t>
   </si>
   <si>
     <t>double</t>
@@ -232,7 +232,7 @@
     <t>RI economic nexus gross receipts threshold - $100,000</t>
   </si>
   <si>
-    <t>ri_state_tax_rate</t>
+    <t>state_tax_rate</t>
   </si>
   <si>
     <t>0.070</t>
@@ -241,7 +241,7 @@
     <t>RI corporate income tax rate - 7% flat rate (R.I. Gen. Laws § 44-11-2)</t>
   </si>
   <si>
-    <t>ri_transaction_threshold</t>
+    <t>transaction_threshold</t>
   </si>
   <si>
     <t>integer</t>
